--- a/Messaging_Workflow_Automation_Test_Plan.xlsx
+++ b/Messaging_Workflow_Automation_Test_Plan.xlsx
@@ -2210,12 +2210,12 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>That worker enrolled on an opportunity with a Registration Form</t>
+          <t>That worker enrolled on an opportunity whose apps belong to THIS HQ domain</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Needed ONLY by the conditional-alert cases (TC-CAL-003/005), which fire on a form submission. Broadcasts, keywords, consent and channel cases need nothing but a PersonalID user with a channel - which is why they were built first. Learn/assessment progress lives on OpportunityAccess, so it cannot be inherited from another opportunity.</t>
+          <t>Two requirements, and the second is easy to miss. (a) A Registration Form in the deliver app, needed ONLY by the conditional-alert cases (TC-CAL-003/005), which fire on a form submission - broadcasts, keywords, consent and channel cases need nothing but a PersonalID user with a channel, which is why they were built first; learn/assessment progress lives on OpportunityAccess and cannot be inherited from another opportunity. (b) The opportunity's learn and deliver apps must come from the SAME HQ domain the messaging is driven from: 'Request Messaging Consent' enumerates users linked to the domain through those apps, so a worker on an opportunity pointing elsewhere is never a Connect messaging user here - the action reports 'No channels created' and no channel can ever be made for them. Diagnosed on staging 2026-08-12.</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -2546,7 +2546,7 @@
       <c r="G3" s="9" t="inlineStr"/>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Manual case 'Connect channel 1'. One-shot per (worker, HQ domain) and therefore not repeatable: ConnectID's CreateChannelView is get_or_create on (server, connect_user, channel_source), and channel_source is the HQ domain, which we do not vary. Run when onboarding a new worker.</t>
+          <t>Manual case 'Connect channel 1'. WHY IT IS NOT RUN EVERY TIME (as of 2026-08-12): ConnectID's CreateChannelView is get_or_create on (server, connect_user, channel_source), and channel_source is the HQ domain, which we do not vary. So the FIRST consent request for a worker creates the channel and fires the one-shot 'New Channel' push; every later request returns the existing channel, creates nothing and sends no push. Reusing one worker therefore means this case can pass exactly once and would be permanently red afterwards, which is worse than not having it. It is written to SKIP with a reason once the worker has a channel, and TC-CHN-001b covers the repeat behaviour on every run. HOW IT BECOMES A PER-RUN TEST: automate learn + assessment on the device, and each run can onboard a brand new worker - PersonalID signup is already automated (login_signup_success.yaml creates accounts in the +7426 range) and invitation is automated (ConnectWorkersPage.invite_workers), so a fresh worker gives a fresh channel and a fresh push and this case runs green every time. Learn/assessment is the only missing link; legacy Appium had it in pages/mobile_pages/learn_app_page.py to port, and porting it would also remove the same manual prerequisite from the tasking suite.</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       <c r="G4" s="9" t="inlineStr"/>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>The repeatable half of 'Connect channel 1', and the more valuable regression guard: it is what stops a duplicate channel appearing every time consent is re-requested.</t>
+          <t>The repeatable half of 'Connect channel 1', and the more valuable regression guard day to day: it is what stops a duplicate channel appearing every time consent is re-requested. Runs on every run regardless of worker state, which is exactly what TC-CHN-001a cannot do until learn and assessment are automated - see its note.</t>
         </is>
       </c>
     </row>

--- a/Messaging_Workflow_Automation_Test_Plan.xlsx
+++ b/Messaging_Workflow_Automation_Test_Plan.xlsx
@@ -2661,13 +2661,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>M3 messaging_empty_state.yaml</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>messaging_empty_state.yaml</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Needs the dedicated no-channel worker (prerequisite #3). Legacy verify_channel_list() accepts empty OR populated, so it never actually pins this state.</t>
+          <t>Legacy verify_channel_list() accepts empty OR populated, so it pins neither state. Verified on staging against Message Automation User, which is in no channels. Doubles as the cheapest way to ask whether an account has a channel yet - it passes only if the account is in none - which is how it was used to confirm TC-CHN-001a's one-shot moment had not been spent.</t>
         </is>
       </c>
     </row>

--- a/Messaging_Workflow_Automation_Test_Plan.xlsx
+++ b/Messaging_Workflow_Automation_Test_Plan.xlsx
@@ -2661,17 +2661,13 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>messaging_empty_state.yaml</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
+          <t>M3 messaging_empty_state.yaml</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Legacy verify_channel_list() accepts empty OR populated, so it pins neither state. Verified on staging against Message Automation User, which is in no channels. Doubles as the cheapest way to ask whether an account has a channel yet - it passes only if the account is in none - which is how it was used to confirm TC-CHN-001a's one-shot moment had not been spent.</t>
+          <t>Legacy verify_channel_list() accepts empty OR populated, so it pins neither state. The flow is written and passed once (staging, build e008c256) but is NOT currently reproducible: it needs an account that has never been in ANY channel on ANY domain, and no such account is reserved. Message Automation User qualified until it gained a channel; Deb Test 8/12 already carries channels from other domains (connetqa-prod, connectqa). This is a fragile resource by nature - any bulk consent request on a domain a worker belongs to populates it. Needs a dedicated never-enrolled PersonalID number, or the flow changed to sign UP a fresh account per run, which by definition has no channels.</t>
         </is>
       </c>
     </row>

--- a/Messaging_Workflow_Automation_Test_Plan.xlsx
+++ b/Messaging_Workflow_Automation_Test_Plan.xlsx
@@ -2578,10 +2578,14 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>W3 test_messaging_channel_creation</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr"/>
+          <t>test_messaging_web::test_repeat_consent_request_creates_no_duplicate</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
           <t>The repeatable half of 'Connect channel 1', and the more valuable regression guard day to day: it is what stops a duplicate channel appearing every time consent is re-requested. Runs on every run regardless of worker state, which is exactly what TC-CHN-001a cannot do until learn and assessment are automated - see its note.</t>
@@ -2699,10 +2703,14 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>M1 messaging_channel_list.yaml</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr"/>
+          <t>messaging_broadcast.yaml</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
           <t>item_channel.xml. The tappable target is itemRootLayout, not tvChannelName - tapping the name alone does nothing.</t>
@@ -2816,10 +2824,14 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>M1 messaging_channel_list.yaml</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
+          <t>messaging_broadcast.yaml</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Legacy open_channel_on_message() asserts only that MESSAGE_INPUT is displayed.</t>
@@ -4003,10 +4015,14 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>W3 test_messaging_channel_creation</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_consent_gates_message_delivery + messaging_unsubscribe_only.yaml</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Asserted on the WEB side, not by proving absence on a device: SendServerConnectMessage returns 400 NO_USER_CONSENT for an unconsented channel, so there is a definite signal instead of an arbitrary wait. Needs two run_flows() calls with the send between them - one build cannot be paused midway.</t>
@@ -4131,10 +4147,14 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>W3 test_messaging_channel_creation</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_consent_gates_message_delivery + messaging_consent_delivery.yaml</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Pairs with TC-SUB-004: on its own, TC-SUB-004 would still pass if delivery were broken permanently. Same reasoning the tasking plan used for its blocked/unblocked visit pair.</t>
@@ -4379,10 +4399,14 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>W1 test_messaging_conditional_alerts</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>messaging_broadcast.yaml</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
           <t>BaseDrawerController, fed by ConnectMessagingDatabaseHelper.getUnviewedMessages().</t>
@@ -4463,10 +4487,14 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Manual only</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_message_push_opens_the_thread + messaging_push_deeplink.yaml</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
           <t>MANUAL by decision (2026-08-12), not by omission. The case needs a message to arrive while the app is backgrounded, but every BrowserStack build starts from a fresh install and cannot be paused, so the web half must send before the device boots - by sign-in the message is already queued and arrives on first sync, never as a push. The ordering would need two builds with a send between, and the second reinstalls and wipes the session. Automatable on a local emulator, where the session persists, if it is ever judged worth the CI cost.</t>

--- a/Messaging_Workflow_Automation_Test_Plan.xlsx
+++ b/Messaging_Workflow_Automation_Test_Plan.xlsx
@@ -3289,10 +3289,14 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>W1 test_messaging_conditional_alerts</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_conditional_alert_reaches_the_channel + messaging_conditional_alert.yaml</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Manual 'Connect message3'; legacy Messaging_2's mobile half. The entity id is the join between the HQ condition and the mobile submission - it must be unique per run.</t>
@@ -3370,10 +3374,14 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>W1 test_messaging_conditional_alerts</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_conditional_alert_survey_is_answerable + messaging_conditional_alert_survey.yaml</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Manual 'Connect message4'; legacy Messaging_3. Same hardcoded-questions gap as TC-BRD-003.</t>

--- a/Messaging_Workflow_Automation_Test_Plan.xlsx
+++ b/Messaging_Workflow_Automation_Test_Plan.xlsx
@@ -2665,13 +2665,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>M3 messaging_empty_state.yaml</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_channel_list_shows_empty_state + messaging_empty_state.yaml</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Legacy verify_channel_list() accepts empty OR populated, so it pins neither state. The flow is written and passed once (staging, build e008c256) but is NOT currently reproducible: it needs an account that has never been in ANY channel on ANY domain, and no such account is reserved. Message Automation User qualified until it gained a channel; Deb Test 8/12 already carries channels from other domains (connetqa-prod, connectqa). This is a fragile resource by nature - any bulk consent request on a domain a worker belongs to populates it. Needs a dedicated never-enrolled PersonalID number, or the flow changed to sign UP a fresh account per run, which by definition has no channels.</t>
+          <t>The flow existed and was registered but nothing ran it - the only reference in the suite was a comment - so this needed a test wrapper as well as an account. Runs as MAESTRO_MESSAGING_EMPTY_STATE, a reserved pair (prod 4376447 / staging 4376448) that must never be invited to a channel or an opportunity: a channel cannot be undone, so one consent request retires this case permanently. Verified on prod, build 842ed35d. A failure here most likely means the account picked up a channel rather than that the empty state is broken.</t>
         </is>
       </c>
     </row>
@@ -2750,10 +2754,14 @@
           <t>Shared precondition step (all flows)</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Not a user-facing case - a guard. Without it, a key-sync failure and a genuine delivery failure look identical, and we would chase a phantom product bug. MessagingChannelsKeySyncWorker backfills keys for consented keyless channels.</t>
+          <t>Already covered, no separate flow needed: the sequence this case describes - open the channel, type into etMessage, assert imgSendMessage appears - occurs 16 times across 6 messaging flows, before every send. That is exactly the guard the case asks for.</t>
         </is>
       </c>
     </row>
@@ -2786,13 +2794,17 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>M2 messaging_subscription.yaml</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_subscribed_channels_sort_before_unsubscribed + messaging_subscription.yaml</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>ChannelAdapter.setChannels. Cheap to assert once TC-SUB-001 has produced an unsubscribed channel in the same session.</t>
+          <t>Needs no hand-prepared account. The worker holds several channels and all are subscribed, so the flow unsubscribes a spare itself and restores it, and repairs the state if a previous run died mid-way. The spare is never the channel the delivery tests send into. It asserts position BEFORE and after: the first spare tried sorted last, so unsubscribing it moved nothing and the case would have passed without observing a sort at all. The within-subscribed order is not stable day to day, so that starting-order assert is what keeps a changed order loud rather than quiet.</t>
         </is>
       </c>
     </row>
@@ -3081,13 +3093,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>W2 test_messaging_broadcasts</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_broadcast_connect_survey_is_answerable + messaging_survey.yaml</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>GAP vs legacy. The manual outcome requires 'Form should get submit and able to verify it on the submit history'; legacy never checks HQ received anything, so a survey that renders but never submits would pass today.</t>
+          <t>Asserted in the same test that answers the survey rather than as a separate run: one device build proves both. Submissions are attributed to the Connect user id, not the PersonalID mobile worker - searching by mobile worker returns nothing while the row is sitting there, which is why this looked blocked. The search is bounded by a timestamp taken before the send, so a previous run's submission cannot satisfy it.</t>
         </is>
       </c>
     </row>
@@ -3416,13 +3432,17 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>W1 test_messaging_conditional_alerts</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_conditional_alert_survey_is_answerable + messaging_conditional_alert_survey.yaml</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>GAP vs legacy - same as TC-BRD-004.</t>
+          <t>Same submit-history check as TC-BRD-004. Matched on the full survey_form breadcrumb rather than 'Registration Form': this flow also submits a Delivery App Registration Form to fire the alert, and a loose match would assert on that one instead.</t>
         </is>
       </c>
     </row>
@@ -3701,13 +3721,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>W4 test_messaging_keywords</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_keyword_returns_a_survey_that_is_answerable + messaging_keyword_survey.yaml</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Manual 'Connect message6'.</t>
+          <t>Was never actually written - the hybrid module's docstring claimed it, but only TC-KWD-002 existed. The flow is the send half of messaging_keyword.yaml followed by the answering half of messaging_survey.yaml. Worth its own case: TC-KWD-002's reply is a single canned message, whereas each question here arrives only after the previous is answered.</t>
         </is>
       </c>
     </row>
@@ -3739,13 +3763,17 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>W4 test_messaging_keywords</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr"/>
+          <t>test_messaging_hybrid::test_keyword_returns_a_survey_that_is_answerable + messaging_keyword_survey.yaml</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Explicit in the manual outcome for 'Connect message6'.</t>
+          <t>Same submit-history check as TC-BRD-004, asserted in the same run as TC-KWD-004.</t>
         </is>
       </c>
     </row>
